--- a/order_forms/046_personalized_notebook_order_form--order_forms.xlsx
+++ b/order_forms/046_personalized_notebook_order_form--order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>order_comments</t>
+          <t>order_comments_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Order Comments</t>
+          <t>Order Comments 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>order_notes</t>
+          <t>order_notes_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Order Notes</t>
+          <t>Order Notes 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>customer_name</t>
+          <t>customer_name_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Customer Name</t>
+          <t>Customer Name 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>customer_email</t>
+          <t>customer_email_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Customer Email</t>
+          <t>Customer Email 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>customer_phone</t>
+          <t>customer_phone_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Customer Phone</t>
+          <t>Customer Phone 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>order_notes</t>
+          <t>order_notes_3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Order Notes</t>
+          <t>Order Notes 3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>order_comments</t>
+          <t>order_comments_3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Order Comments</t>
+          <t>Order Comments 3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>order_status</t>
+          <t>order_status_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Order Status</t>
+          <t>Order Status 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1262,7 +1262,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>order_status_choices</t>
+          <t>order_status_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1279,7 +1279,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>order_status_choices</t>
+          <t>order_status_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
